--- a/quizzes/014_sewing_machine_parts_quiz--quizzes.xlsx
+++ b/quizzes/014_sewing_machine_parts_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is a primary function of a sewing machine?</t>
+          <t>What is the primary function of a sewing machine?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,64 +589,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often is the presser foot used?</t>
+          <t>What is the primary function of the presser foot?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the primary function of the presser foot?</t>
+          <t>What is a presser bar?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>answer_6</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is a sewing machine part?</t>
+          <t>What is a thread guide used for?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer_7</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the bobbin winder used for?</t>
+          <t>How often is the presser bar used?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>answer_8</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often is the bobbin winder used?</t>
+          <t>What is the primary purpose of a thread guide?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_9</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is a presser bar?</t>
+          <t>What is a thread take-up lever used for?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>answer_10</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is a presser foot?</t>
+          <t>What is a presser foot assembly?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_11</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often is the presser bar used?</t>
+          <t>What is the primary function of a presser bar?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>answer_12</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is a thread take-up lever?</t>
+          <t>How often is a thread guide used?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>answer_13</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is a presser foot assembly?</t>
+          <t>What is the primary function of a thread guide?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>answer_14</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the primary purpose of a presser bar?</t>
+          <t>Question 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>answer_15</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How often is a thread take-up lever used?</t>
+          <t>What is a presser foot used for?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>answer_16</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is a thread guide?</t>
+          <t>How often is a thread take-up used?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>answer_17</t>
+          <t>question_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is a thread guide used for?</t>
+          <t>What is a thread take-up used for?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>answer_18</t>
+          <t>question_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is a presser bar for?</t>
+          <t>What is a presser bar's primary function?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -934,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>answer_19</t>
+          <t>question_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is a thread guide used for?</t>
+          <t>What is a presser foot's primary function?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,18 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>answer_20</t>
+          <t>question_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the primary function of a thread guide?</t>
+          <t>What is a thread guide's secondary function?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,41 +980,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>answer_21</t>
+          <t>question_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is a thread guide used for?</t>
+          <t>What is a thread take-up's primary function?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>answer_22</t>
+          <t>question_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is a presser bar?</t>
+          <t>Question 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>answer_23</t>
+          <t>question_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is a presser foot?</t>
+          <t>How often is a thread take-up lever used?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1049,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>answer_24</t>
+          <t>question_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is a thread take-up?</t>
+          <t>What is a thread guide's primary function?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1072,18 +1072,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>answer_25</t>
+          <t>question_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is a thread take-up lever?</t>
+          <t>Question 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,177 +1126,177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>to_sew_fabric</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>To sew fabric</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>to_wind_bobbins</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>To wind bobbins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>To lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>answer_2_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sewing_machine_base</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sewing Machine Base</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>answer_2_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bobbin</t>
+          <t>sewing_machine_base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bobbin</t>
+          <t>Sewing Machine Base</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>answer_2_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hook</t>
+          <t>bobbin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Bobbin</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>hook</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Hook</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>answer_3_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,585 +1313,585 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>guides_the_fabric</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Guides the fabric</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>answer_4_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>raises_and_lowers_the_presser_bar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Raises and lowers the presser bar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>a_bar_for_the_presser_foot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>A bar for the presser foot</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>guides_the_fabric</t>
+          <t>a_part_of_the_presser_foot_assembly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Guides the fabric</t>
+          <t>A part of the presser foot assembly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>answer_5_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raises_and_lowers_the_presser_bar</t>
+          <t>a_device_for_guiding_the_presser_foot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raises and lowers the presser bar</t>
+          <t>A device for guiding the presser foot</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>answer_6_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>a_machine_for_sewing</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A machine for sewing</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>answer_6_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>a_tool_for_sewing</t>
+          <t>for_the_bobbin_winder</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A tool for sewing</t>
+          <t>For the bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>answer_6_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>a_device_for_sewing</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A device for sewing</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>answer_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>a_part_for_sewing</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A part for sewing</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>answer_7_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>to_wind_bobbins</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>To wind bobbins</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>answer_7_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>to_wind_threads</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>To wind threads</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>answer_7_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>to_wind_yarns</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>To wind yarns</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>answer_8_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>answer_8_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>answer_8_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>To lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>answer_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>answer_9_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>a_bar_for_the_presser_foot</t>
+          <t>used_to_guide_the_bobbin_winder</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A bar for the presser foot</t>
+          <t>Used to guide the bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>answer_9_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>a_part_of_the_presser_foot_assembly</t>
+          <t>used_to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A part of the presser foot assembly</t>
+          <t>Used to lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>answer_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>a_device_for_guiding_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A device for guiding the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>answer_10_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>the_assembly_of_the_presser_bar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>The assembly of the presser bar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>answer_10_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>a_foot_for_guiding_the_presser_bar</t>
+          <t>the_assembly_of_the_presser_foot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A foot for guiding the presser bar</t>
+          <t>The assembly of the presser foot</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>answer_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>a_device_for_the_presser_foot_assembly</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A device for the presser foot assembly</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>answer_11_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>to_guide_the_presser_foot</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>To guide the presser foot</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>answer_11_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>to_lower_the_presser_bar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>To lower the presser bar</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>answer_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>answer_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>answer_12_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>answer_12_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>used_to_guide_the_presser_bar</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Used to guide the presser bar</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>answer_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>used_to_guide_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Used to guide the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>answer_13_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>answer_13_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>the_assembly_of_the_presser_bar</t>
+          <t>to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The assembly of the presser bar</t>
+          <t>To lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>answer_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>the_assembly_of_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The assembly of the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>answer_14_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>for_the_bobbin_winder</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>For the bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>answer_14_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,500 +1908,500 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>answer_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>to_lower_the_presser_bar</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>To lower the presser bar</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>answer_15_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>to_lower_the_presser_bar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>To lower the presser bar</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>answer_15_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>to_raise_the_presser_bar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>To raise the presser bar</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>answer_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>answer_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>answer_16_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>answer_16_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>for_the_bobbin_winder</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>For the bobbin winder</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>answer_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>for_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>For the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>answer_17_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>for_the_bobbin_winder</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>For the bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>answer_17_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>to_guide_the_presser_bar</t>
+          <t>for_the_presser_foot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>To guide the presser bar</t>
+          <t>For the presser foot</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>answer_17_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>to_lower_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>To lower the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>answer_18_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>to_guide_the_presser_foot</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>To guide the presser foot</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>answer_18_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>for_the_bobbin_winder</t>
+          <t>to_lower_the_presser_bar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>For the bobbin winder</t>
+          <t>To lower the presser bar</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>answer_18_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>for_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>For the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>answer_19_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>answer_19_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>to_guide_the_presser_bar</t>
+          <t>to_raise_the_presser_bar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>To guide the presser bar</t>
+          <t>To raise the presser bar</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>answer_19_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>to_lower_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>To lower the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>answer_20_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>to_guide_the_presser_foot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>To guide the presser foot</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>answer_20_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>to_guide_the_presser_bar</t>
+          <t>to_lower_the_presser_bar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>To guide the presser bar</t>
+          <t>To lower the presser bar</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>answer_20_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>to_lower_the_presser_foot</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>To lower the presser foot</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>answer_21_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>to_guide_the_bobbin_winder</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>To guide the bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>answer_21_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>for_the_presser_foot</t>
+          <t>to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>For the presser foot</t>
+          <t>To lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>answer_21_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>for_the_presser_bar</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>For the presser bar</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>answer_22_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>a_bar_for_the_presser_foot</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A bar for the presser foot</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>answer_22_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>a_part_of_the_presser_foot_assembly</t>
+          <t>to_raise_the_presser_bar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A part of the presser foot assembly</t>
+          <t>To raise the presser bar</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>answer_22_choices</t>
+          <t>question_23_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>a_device_for_guiding_the_presser_foot</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A device for guiding the presser foot</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>answer_23_choices</t>
+          <t>question_23_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>answer_23_choices</t>
+          <t>question_23_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>a_foot_for_guiding_the_presser_bar</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>A foot for guiding the presser bar</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>answer_23_choices</t>
+          <t>question_23_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>a_device_for_the_presser_bar_assembly</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A device for the presser bar assembly</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>answer_24_choices</t>
+          <t>question_24_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2418,41 +2418,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>answer_24_choices</t>
+          <t>question_24_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>for_the_bobbin_winder</t>
+          <t>to_guide_the_presser_bar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>For the bobbin winder</t>
+          <t>To guide the presser bar</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>answer_24_choices</t>
+          <t>question_24_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>for_the_presser_foot</t>
+          <t>to_lower_the_presser_foot</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>For the presser foot</t>
+          <t>To lower the presser foot</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>answer_25_choices</t>
+          <t>question_25_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2469,34 +2469,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>answer_25_choices</t>
+          <t>question_25_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>used_to_guide_the_bobbin_winder</t>
+          <t>to_guide_the_presser_foot</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Used to guide the bobbin winder</t>
+          <t>To guide the presser foot</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>answer_25_choices</t>
+          <t>question_25_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>used_to_lower_the_presser_foot</t>
+          <t>to_lower_the_presser_bar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Used to lower the presser foot</t>
+          <t>To lower the presser bar</t>
         </is>
       </c>
     </row>
